--- a/testakten/scheidungsdrama/xlsx/versorgungsausgleich_anwartschaften.xlsx
+++ b/testakten/scheidungsdrama/xlsx/versorgungsausgleich_anwartschaften.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>Versorgungsausgleich — Wagenknecht / Luetzelberg (§§ 1 ff. VersAusglG)</t>
+          <t>Versorgungsausgleich — Hanna Trüffelberch / Franz Trüffelberch (§§ 1 ff. VersAusglG)</t>
         </is>
       </c>
     </row>
@@ -637,7 +637,7 @@
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>Vera</t>
+          <t>Hanna</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>Vera</t>
+          <t>Hanna</t>
         </is>
       </c>
       <c r="D8" s="13" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>Theo</t>
+          <t>Franz</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="C10" s="16" t="inlineStr">
         <is>
-          <t>Theo</t>
+          <t>Franz</t>
         </is>
       </c>
       <c r="D10" s="17" t="inlineStr">
@@ -762,7 +762,7 @@
     <row r="14">
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Vera: voraussichtliche Altersrente gesamt (Regelaltersgrenze 67)</t>
+          <t>Hanna: voraussichtliche Altersrente gesamt (Regelaltersgrenze 67)</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
@@ -779,7 +779,7 @@
     <row r="15">
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>Vera: Ehezeitanteil (01.08.2008–31.01.2026)</t>
+          <t>Hanna: Ehezeitanteil (01.08.2008–31.01.2026)</t>
         </is>
       </c>
       <c r="D15" s="16" t="inlineStr">
@@ -796,7 +796,7 @@
     <row r="16">
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Hälftige Teilung: Zuweisung an Theo</t>
+          <t>Hälftige Teilung: Zuweisung an Franz</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
@@ -812,7 +812,7 @@
     <row r="17">
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Vera: Verbleibender AKNS-Anspruch nach Ausgleich</t>
+          <t>Hanna: Verbleibender AKNS-Anspruch nach Ausgleich</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
@@ -822,14 +822,14 @@
       </c>
       <c r="F17" s="11" t="inlineStr">
         <is>
-          <t>Vera verliert Ehezeitanteil hälftig</t>
+          <t>Hanna verliert Ehezeitanteil hälftig</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="19" t="inlineStr">
         <is>
-          <t>Kapitalwert des Ausgleichsbetrags (Theo erhält bei AKNS)</t>
+          <t>Kapitalwert des Ausgleichsbetrags (Franz erhält bei AKNS)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -857,12 +857,12 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Auswirkung Vera</t>
+          <t>Auswirkung Hanna</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>Auswirkung Theo</t>
+          <t>Auswirkung Franz</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="D22" s="22" t="inlineStr">
         <is>
-          <t>Gibt AKNS-Anteil: ca. 1.072 EUR/Mon. ab; erhält GRV-Anteil Theo</t>
+          <t>Gibt AKNS-Anteil: ca. 1.072 EUR/Mon. ab; erhält GRV-Anteil Franz</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>Gibt AKNS ab; GRV verbleibt bei Vera</t>
+          <t>Gibt AKNS ab; GRV verbleibt bei Hanna</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
